--- a/registration_forms/029_field_trip_consent_and_intake_form--registration_forms.xlsx
+++ b/registration_forms/029_field_trip_consent_and_intake_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1347,17 +1347,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>student_allergies_choices</t>
+          <t>emergency_contact_name_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shellfish</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shellfish</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_name_choices</t>
+          <t>student_participants_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>student_participants_choices</t>
+          <t>student_bus_passengers_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>student_bus_passengers_choices</t>
+          <t>student_conduct_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>student_conduct_choices</t>
+          <t>transportation_method_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>school_bus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>School Bus</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>school_bus</t>
+          <t>parent/guardian_pickup</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>School Bus</t>
+          <t>Parent/Guardian Pickup</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>parent/guardian_pickup</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parent/Guardian Pickup</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>transportation_method_choices</t>
+          <t>student_drop_off_information_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>student_drop_off_information_choices</t>
+          <t>parent_consent_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>parent_consent_choices</t>
+          <t>student_medical_condition_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>student_medical_condition_choices</t>
+          <t>student_medical_allergies_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>student_medical_allergies_choices</t>
+          <t>student_medical_aid_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>student_medical_aid_choices</t>
+          <t>student_medical_medication_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>student_medical_medication_choices</t>
+          <t>student_medical_device_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1760,27 +1760,10 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>student_medical_device_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
